--- a/wbfm/notebooks/paper/revisions/fig3/intrinsic_categories.xlsx
+++ b/wbfm/notebooks/paper/revisions/fig3/intrinsic_categories.xlsx
@@ -453,12 +453,12 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AQR</t>
+          <t>(SAAV)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_False_diff_True</t>
+          <t>gcamp_True_immob_False_same_sign_True_diff_True</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -497,12 +497,12 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SAAV</t>
+          <t>AQR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_True_diff_True</t>
+          <t>gcamp_True_immob_False_same_sign_False_diff_True</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DD01</t>
+          <t>RMEV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,12 +541,12 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IL2</t>
+          <t>DD01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_False_diff_True</t>
+          <t>gcamp_True_immob_False_same_sign_True_diff_True</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -563,12 +563,12 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>RMEV</t>
+          <t>IL2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_True_diff_True</t>
+          <t>gcamp_True_immob_False_same_sign_False_diff_True</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>URAD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>URAD</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,12 +629,12 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>VB01</t>
+          <t>(DA01)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -695,12 +695,12 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SIAD</t>
+          <t>RME</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -717,12 +717,12 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>RME</t>
+          <t>RMDD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -739,12 +739,12 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>VB02</t>
+          <t>RIV</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -761,12 +761,12 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>RIV</t>
+          <t>VB02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -783,12 +783,12 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>RMDD</t>
+          <t>RID</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -827,12 +827,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AVB</t>
+          <t>DB01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -849,12 +849,12 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>AVE</t>
+          <t>(DB02)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>DB01</t>
+          <t>(RIB)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -893,7 +893,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>DB02</t>
+          <t>(SIAD)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>DA01</t>
+          <t>(VB01)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>gcamp_True_immob_True_same_sign_True_diff_False</t>
+          <t>gcamp_True_immob_False_same_sign_True_diff_False</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>RIB</t>
+          <t>RIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>RID</t>
+          <t>VB03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>RIA</t>
+          <t>AVB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>VB03</t>
+          <t>AVE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>RMED</t>
+          <t>AVA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>RIS</t>
+          <t>RMDV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>BAG</t>
+          <t>URYD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>URYD</t>
+          <t>URYV</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>URYV</t>
+          <t>BAG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1157,7 +1157,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>RMDV</t>
+          <t>RIS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>AVA</t>
+          <t>RMED</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1223,7 +1223,7 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>AWB</t>
+          <t>(AWB)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
